--- a/Day1/BiswayanNath_ManualTesting.xlsx
+++ b/Day1/BiswayanNath_ManualTesting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\biswa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B4DF72-5C67-4A8F-9690-075826613AFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEED953-F5B3-4ED3-ADBD-4847A235564D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="RTM" sheetId="5" r:id="rId5"/>
     <sheet name="Summary" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="201">
   <si>
     <t>Issue Type</t>
   </si>
@@ -86,13 +86,7 @@
     <t>Test Case Details</t>
   </si>
   <si>
-    <t>TS_Website_01</t>
-  </si>
-  <si>
     <t>Functional Testing</t>
-  </si>
-  <si>
-    <t>TS_RedBus_01</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -123,154 +117,15 @@
  Iteration 1</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Candara"/>
-      </rPr>
-      <t xml:space="preserve">Actual Result Iteration 2
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Candara"/>
-      </rPr>
-      <t xml:space="preserve">(to be updated only if test case failed in Iteration 1) </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Candara"/>
-      </rPr>
-      <t xml:space="preserve">Status
- Iteration 2
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Candara"/>
-      </rPr>
-      <t>(to be updated only if test case failed in Iteration 1)</t>
-    </r>
-  </si>
-  <si>
     <t>Comments</t>
   </si>
   <si>
     <t>Req: Reference</t>
   </si>
   <si>
-    <t>&lt;Sequence number&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Identify test scenarios&gt;</t>
-  </si>
-  <si>
-    <t>&lt;This cell specifies the state a system and its environment must be in before this specific test case can be run&gt;</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="12"/>
-        <rFont val="Candara"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;This cell describes </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color indexed="12"/>
-        <rFont val="Candara"/>
-        <family val="2"/>
-      </rPr>
-      <t>what</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="12"/>
-        <rFont val="Candara"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to test for i.e. the condition which is being tested for&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="12"/>
-        <rFont val="Candara"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;This cell describes </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color indexed="12"/>
-        <rFont val="Candara"/>
-        <family val="2"/>
-      </rPr>
-      <t>how</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="12"/>
-        <rFont val="Candara"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to test i.e. the detailed testing procedure&gt;</t>
-    </r>
-  </si>
-  <si>
-    <t>&lt;Mention test data to be used&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Describe the expected test result&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Describe the actual test result after execution of test cases. In case screenshots need to be attached to substantiate the test result, use the references tab.&gt;</t>
-  </si>
-  <si>
-    <t>Status of the test case whether it got passed/ failed/Hold  in interation 1.</t>
-  </si>
-  <si>
-    <t>&lt;Describe the actual test result after execution of test cases second time. In case screenshots need to be attached to substantiate the test result, use the references tab.&gt;</t>
-  </si>
-  <si>
-    <t>New status of test case after it failed in Iteration 1.</t>
-  </si>
-  <si>
-    <t>TC_Website_01</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>TC_RedBus_03</t>
-  </si>
-  <si>
     <t>Defect Id.</t>
   </si>
   <si>
@@ -289,36 +144,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>DF_LandingPage_01</t>
-  </si>
-  <si>
-    <t>Landing Page</t>
-  </si>
-  <si>
-    <t>Sign Up (Create Account)option is not available on landing page.</t>
-  </si>
-  <si>
-    <t>abc@capgemini.com</t>
-  </si>
-  <si>
-    <t>To do</t>
-  </si>
-  <si>
-    <t>DF_RedBus_01</t>
-  </si>
-  <si>
-    <t>Login functionality</t>
-  </si>
-  <si>
-    <t>invalid data can be accepted in login</t>
-  </si>
-  <si>
-    <t>deepa@gmail.com</t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
     <t>BR_ID</t>
   </si>
   <si>
@@ -337,57 +162,9 @@
     <t>DR_ID</t>
   </si>
   <si>
-    <t>BR_Website_01</t>
-  </si>
-  <si>
-    <t>TR_Website_01</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>TC_Website_02</t>
-  </si>
-  <si>
-    <t>TC_Website_03</t>
-  </si>
-  <si>
-    <t>BR_RedBus_01</t>
-  </si>
-  <si>
-    <t>TR_RedBus_01</t>
-  </si>
-  <si>
-    <t>TC_RedBus_01</t>
-  </si>
-  <si>
-    <t>TC_RedBus_02</t>
-  </si>
-  <si>
-    <t>TC_RedBus_04</t>
-  </si>
-  <si>
-    <t>BR_RedBus_02</t>
-  </si>
-  <si>
-    <t>TR_RedBus_02</t>
-  </si>
-  <si>
-    <t>TS_RedBus_02</t>
-  </si>
-  <si>
-    <t>TC_RedBus_05</t>
-  </si>
-  <si>
-    <t>TC_RedBus_06</t>
-  </si>
-  <si>
-    <t>TC_RedBus+07</t>
-  </si>
-  <si>
-    <t>TC_RedBus_08</t>
-  </si>
-  <si>
     <t>TEST EXECUTION SUMMARY</t>
   </si>
   <si>
@@ -415,18 +192,6 @@
     <t>Fail Percentage</t>
   </si>
   <si>
-    <t>Complition Percentage</t>
-  </si>
-  <si>
-    <t>Universal  Class</t>
-  </si>
-  <si>
-    <t>Sign In</t>
-  </si>
-  <si>
-    <t>Sign Up</t>
-  </si>
-  <si>
     <t>Holiday Package Booking</t>
   </si>
   <si>
@@ -439,9 +204,6 @@
     <t>Verify search with invalid input data</t>
   </si>
   <si>
-    <t>Verify auto-suggestions for destination</t>
-  </si>
-  <si>
     <t>Sub story 3</t>
   </si>
   <si>
@@ -484,9 +246,6 @@
     <t>Verify recently viewed packages section displays after user interaction</t>
   </si>
   <si>
-    <t>Verify packages are grouped with location filters</t>
-  </si>
-  <si>
     <t>Epic 4</t>
   </si>
   <si>
@@ -521,11 +280,6 @@
   </si>
   <si>
     <t>REQ_MakeMyTrip_05</t>
-  </si>
-  <si>
-    <t>1. Verify search with valid input data.
-2. Verify search with invalid input data.
-3. Verify auto-suggestions for destination.</t>
   </si>
   <si>
     <t>Validate that users can search for holiday packages using valid inputs and receive accurate results.</t>
@@ -633,30 +387,7 @@
 4. 2 Adults, 1 Room</t>
   </si>
   <si>
-    <t>1. Chennai
-2. Kerala
-3. 12 May 2023
-4. 2 Adults, 1 Room</t>
-  </si>
-  <si>
-    <t>1. Chennai
-2. 12 May 2023
-3. 2 Adults, 1 Room
-4. Ker</t>
-  </si>
-  <si>
-    <t>To verify auto-suggestions for destination.</t>
-  </si>
-  <si>
-    <t>1. Enter source location, departure date and number of rooms and guests.
-2. Enter destination location partially and select from suggestions.
-3. Click on search button.</t>
-  </si>
-  <si>
     <t>To verify clicking “Visa Free Packages” displays predefined destinations list.</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>To verify clicking a destination loads relevant holiday packages.</t>
@@ -681,13 +412,7 @@
     <t>It should not accept the specified details.</t>
   </si>
   <si>
-    <t>It should open a trip package with specified details, autofilling the destination location.</t>
-  </si>
-  <si>
     <t>It should display a list of predefined destinations.</t>
-  </si>
-  <si>
-    <t>It should display details of a Visa Free Holiday Package.</t>
   </si>
   <si>
     <t>To verify UI content (images, labels) loads correctly.</t>
@@ -757,19 +482,7 @@
     <t>To verify recently viewed packages section displays after user interaction.</t>
   </si>
   <si>
-    <t>To verify packages are grouped with location filters.</t>
-  </si>
-  <si>
-    <t>1. Click on the first location filter in the Recently Viewed Packages section.
-2. Click on the first package from the list.</t>
-  </si>
-  <si>
     <t>Verify “Review &amp; Pay / Book Now” CTA works correctly</t>
-  </si>
-  <si>
-    <t>1. Verify recently viewed packages section displays after user interaction.
-2. Verify packages are grouped with location filters.
-3. Verify “Review &amp; Pay / Book Now” CTA works correctly</t>
   </si>
   <si>
     <t>To verify “Review &amp; Pay / Book Now” CTA works correctly.</t>
@@ -786,10 +499,181 @@
     <t>It should open the package details of the last seen package.</t>
   </si>
   <si>
-    <t>It should open the package details of the last seen package for the specified location.</t>
-  </si>
-  <si>
     <t>It should open the review package page for the last seen package.</t>
+  </si>
+  <si>
+    <t>1. Chennai
+2. iaooxoias
+3. 12 May 2026
+4. 2 Adults, 1 Room</t>
+  </si>
+  <si>
+    <t>Completion Percentage</t>
+  </si>
+  <si>
+    <t>TS_MakeMyTrip_01</t>
+  </si>
+  <si>
+    <t>TR_MakeMyTrip_01</t>
+  </si>
+  <si>
+    <t>BR_MakeMyTrip_01</t>
+  </si>
+  <si>
+    <t>BR_MakeMyTrip_02</t>
+  </si>
+  <si>
+    <t>BR_MakeMyTrip_03</t>
+  </si>
+  <si>
+    <t>BR_MakeMyTrip_04</t>
+  </si>
+  <si>
+    <t>BR_MakeMyTrip_05</t>
+  </si>
+  <si>
+    <t>TR_MakeMyTrip_02</t>
+  </si>
+  <si>
+    <t>TR_MakeMyTrip_03</t>
+  </si>
+  <si>
+    <t>TR_MakeMyTrip_04</t>
+  </si>
+  <si>
+    <t>TR_MakeMyTrip_05</t>
+  </si>
+  <si>
+    <t>TS_MakeMyTrip_02</t>
+  </si>
+  <si>
+    <t>TS_MakeMyTrip_03</t>
+  </si>
+  <si>
+    <t>TS_MakeMyTrip_04</t>
+  </si>
+  <si>
+    <t>TS_MakeMyTrip_05</t>
+  </si>
+  <si>
+    <t>It opens a trip package with specified details.</t>
+  </si>
+  <si>
+    <t>It displays a list of predefined destinations.</t>
+  </si>
+  <si>
+    <t>It displays details of a Visa Free Holiday package.</t>
+  </si>
+  <si>
+    <t>It should display details of a Visa Free Holiday package.</t>
+  </si>
+  <si>
+    <t>It displays images and labels of the selected location.</t>
+  </si>
+  <si>
+    <t>It displays a list of cruise categories.</t>
+  </si>
+  <si>
+    <t>It displays the list of all available cruise trips.</t>
+  </si>
+  <si>
+    <t>It opens a Disney Cruise with specified details.</t>
+  </si>
+  <si>
+    <t>It opens a Last Minute Deal which starts 27 days from current date.</t>
+  </si>
+  <si>
+    <t>It opens a Last Minute Deal which starts after the current date.</t>
+  </si>
+  <si>
+    <t>It displays images and labels of the selected package correctly.</t>
+  </si>
+  <si>
+    <t>It opens the package details of the last seen package.</t>
+  </si>
+  <si>
+    <t>It opens the package details of the last seen package for the specified destination.</t>
+  </si>
+  <si>
+    <t>It should open the package details of the last seen package for the specified destination.</t>
+  </si>
+  <si>
+    <t>To verify packages are grouped with destination filters.</t>
+  </si>
+  <si>
+    <t>1. Click on the first destination filter in the Recently Viewed Packages section.
+2. Click on the first package from the list.</t>
+  </si>
+  <si>
+    <t>1. Verify recently viewed packages section displays after user interaction.
+2. Verify packages are grouped with destination filters.
+3. Verify “Review &amp; Pay / Book Now” CTA works correctly</t>
+  </si>
+  <si>
+    <t>Verify packages are grouped with destination filters</t>
+  </si>
+  <si>
+    <t>It opens the review package page for the last seen package.</t>
+  </si>
+  <si>
+    <t>Actual Result Iteration 2</t>
+  </si>
+  <si>
+    <t>Status
+ Iteration 2</t>
+  </si>
+  <si>
+    <t>Verify multiple filters are being applied correctly</t>
+  </si>
+  <si>
+    <t>1. Verify search with valid input data.
+2. Verify search with invalid input data.
+3. Verify multiple filters are being applied correctly.</t>
+  </si>
+  <si>
+    <t>To verify multiple filters are being applied correctly</t>
+  </si>
+  <si>
+    <t>1. Chennai
+2. Kerala
+3. 12 May 2026
+4. 2 Adults, 1 Room
+5. Filters:
+    i. With Flight
+    ii. ₹0 - ₹20000
+    iii. 5 Star</t>
+  </si>
+  <si>
+    <t>1. Enter source location, departure date and number of rooms and guests.
+2. Enter all the filters.
+3. Click on search button.</t>
+  </si>
+  <si>
+    <t>It should open all trip packages with the specified details.</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>The trip packages displayed are not within the specified price range.</t>
+  </si>
+  <si>
+    <t>DF_HolidayPackage_01</t>
+  </si>
+  <si>
+    <t>Multiple filters applied do not enforce price range correctly.</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Make My Trip Application</t>
+  </si>
+  <si>
+    <t>It does not accept the invalid data (destination location) and replaces it with default location.</t>
+  </si>
+  <si>
+    <t>abc@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -826,18 +710,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Candara"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="12"/>
-      <name val="Candara"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <name val="Candara"/>
       <family val="2"/>
@@ -868,21 +755,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Candara"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="12"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
@@ -927,12 +799,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Candara"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Candara"/>
     </font>
     <font>
@@ -994,8 +860,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1016,18 +905,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA8D08D"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1035,12 +912,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD966"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1068,8 +939,20 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1110,21 +993,6 @@
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -1238,13 +1106,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1270,17 +1139,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1293,150 +1155,213 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="81">
+  <dxfs count="90">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2294,7 +2219,7 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
@@ -2302,256 +2227,256 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A2" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="64" t="s">
+      <c r="A2" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="43" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C3" s="65" t="s">
+      <c r="B3" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="44" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="66" t="s">
+      <c r="B4" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="45" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="66" t="s">
+      <c r="B5" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="45" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="46" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="65" t="s">
+      <c r="B7" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="41" customFormat="1">
-      <c r="A8" s="45" t="s">
+    <row r="8" spans="1:3" s="25" customFormat="1">
+      <c r="A8" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="66" t="s">
+      <c r="B8" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="41" customFormat="1">
-      <c r="A9" s="34" t="s">
+    <row r="9" spans="1:3" s="25" customFormat="1">
+      <c r="A9" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" s="66" t="s">
+      <c r="B9" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="41" customFormat="1">
-      <c r="A10" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="67" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="41" customFormat="1">
-      <c r="A11" s="49" t="s">
+    <row r="10" spans="1:3" s="25" customFormat="1">
+      <c r="A10" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="25" customFormat="1">
+      <c r="A11" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="65" t="s">
+      <c r="B11" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="44" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="41" customFormat="1">
-      <c r="A12" s="45" t="s">
+    <row r="12" spans="1:3" s="25" customFormat="1">
+      <c r="A12" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="25" customFormat="1">
+      <c r="A13" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="25" customFormat="1">
+      <c r="A14" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="25" customFormat="1">
+      <c r="A15" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="25" customFormat="1">
+      <c r="A16" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="25" customFormat="1">
+      <c r="A17" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="25" customFormat="1">
+      <c r="A18" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="25" customFormat="1">
+      <c r="A19" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="25" customFormat="1">
+      <c r="A20" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="25" customFormat="1">
+      <c r="A21" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C21" s="48" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="41" customFormat="1">
-      <c r="A13" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" s="66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="41" customFormat="1">
-      <c r="A14" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="67" t="s">
+    <row r="22" spans="1:3" s="25" customFormat="1">
+      <c r="A22" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="49" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="41" customFormat="1">
-      <c r="A15" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="65" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="41" customFormat="1">
-      <c r="A16" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="66" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="41" customFormat="1">
-      <c r="A17" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="66" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="41" customFormat="1">
-      <c r="A18" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="67" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="41" customFormat="1">
-      <c r="A19" s="50" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="68" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="41" customFormat="1">
-      <c r="A20" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="41" customFormat="1">
-      <c r="A21" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>120</v>
-      </c>
-      <c r="C21" s="69" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="41" customFormat="1">
-      <c r="A22" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="B22" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="41" customFormat="1">
-      <c r="A23" s="44"/>
-      <c r="B23" s="42"/>
-    </row>
-    <row r="24" spans="1:3" s="41" customFormat="1">
-      <c r="A24" s="44"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="43"/>
-    </row>
-    <row r="25" spans="1:3" s="41" customFormat="1">
-      <c r="A25" s="44"/>
-      <c r="B25" s="42"/>
-    </row>
-    <row r="26" spans="1:3" s="41" customFormat="1">
-      <c r="A26" s="44"/>
-      <c r="B26" s="42"/>
-    </row>
-    <row r="27" spans="1:3" s="41" customFormat="1">
-      <c r="A27" s="44"/>
-      <c r="B27" s="42"/>
+    <row r="23" spans="1:3" s="25" customFormat="1">
+      <c r="A23" s="28"/>
+      <c r="B23" s="26"/>
+    </row>
+    <row r="24" spans="1:3" s="25" customFormat="1">
+      <c r="A24" s="28"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="27"/>
+    </row>
+    <row r="25" spans="1:3" s="25" customFormat="1">
+      <c r="A25" s="28"/>
+      <c r="B25" s="26"/>
+    </row>
+    <row r="26" spans="1:3" s="25" customFormat="1">
+      <c r="A26" s="28"/>
+      <c r="B26" s="26"/>
+    </row>
+    <row r="27" spans="1:3" s="25" customFormat="1">
+      <c r="A27" s="28"/>
+      <c r="B27" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2571,7 +2496,7 @@
     <col min="6" max="6" width="52.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="45">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="38.25" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -2593,105 +2518,105 @@
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" ht="63.75">
       <c r="A2" s="4" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="7">
         <v>3</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="32" customFormat="1" ht="51">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="19" customFormat="1" ht="51">
       <c r="A3" s="4" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="E3" s="7">
         <v>3</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="32" customFormat="1" ht="51">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="19" customFormat="1" ht="51">
       <c r="A4" s="4" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="E4" s="7">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="32" customFormat="1" ht="51">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="19" customFormat="1" ht="51">
       <c r="A5" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="55" t="s">
-        <v>131</v>
+        <v>76</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>81</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="E5" s="7">
         <v>3</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="32" customFormat="1" ht="51">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="19" customFormat="1" ht="51">
       <c r="A6" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="55" t="s">
-        <v>132</v>
+        <v>77</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>82</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="7">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="32" customFormat="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="19" customFormat="1">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7"/>
@@ -2699,7 +2624,7 @@
       <c r="E7"/>
       <c r="F7"/>
     </row>
-    <row r="8" spans="1:6" s="32" customFormat="1">
+    <row r="8" spans="1:6" s="19" customFormat="1">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
@@ -2707,7 +2632,7 @@
       <c r="E8"/>
       <c r="F8"/>
     </row>
-    <row r="9" spans="1:6" s="32" customFormat="1">
+    <row r="9" spans="1:6" s="19" customFormat="1">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
@@ -2715,7 +2640,7 @@
       <c r="E9"/>
       <c r="F9"/>
     </row>
-    <row r="10" spans="1:6" s="32" customFormat="1">
+    <row r="10" spans="1:6" s="19" customFormat="1">
       <c r="A10"/>
       <c r="B10"/>
       <c r="C10"/>
@@ -2723,7 +2648,7 @@
       <c r="E10"/>
       <c r="F10"/>
     </row>
-    <row r="11" spans="1:6" s="32" customFormat="1">
+    <row r="11" spans="1:6" s="19" customFormat="1">
       <c r="A11"/>
       <c r="B11"/>
       <c r="C11"/>
@@ -2731,7 +2656,7 @@
       <c r="E11"/>
       <c r="F11"/>
     </row>
-    <row r="12" spans="1:6" s="32" customFormat="1">
+    <row r="12" spans="1:6" s="19" customFormat="1">
       <c r="A12"/>
       <c r="B12"/>
       <c r="C12"/>
@@ -2739,7 +2664,7 @@
       <c r="E12"/>
       <c r="F12"/>
     </row>
-    <row r="13" spans="1:6" s="32" customFormat="1">
+    <row r="13" spans="1:6" s="19" customFormat="1">
       <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
@@ -2747,7 +2672,7 @@
       <c r="E13"/>
       <c r="F13"/>
     </row>
-    <row r="14" spans="1:6" s="32" customFormat="1">
+    <row r="14" spans="1:6" s="19" customFormat="1">
       <c r="A14"/>
       <c r="B14"/>
       <c r="C14"/>
@@ -2755,7 +2680,7 @@
       <c r="E14"/>
       <c r="F14"/>
     </row>
-    <row r="15" spans="1:6" s="32" customFormat="1">
+    <row r="15" spans="1:6" s="19" customFormat="1">
       <c r="A15"/>
       <c r="B15"/>
       <c r="C15"/>
@@ -2770,7 +2695,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2784,815 +2709,850 @@
     <col min="9" max="9" width="20.140625" customWidth="1"/>
     <col min="10" max="10" width="23.85546875" customWidth="1"/>
     <col min="11" max="11" width="16.140625" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="87" customHeight="1">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:13" ht="40.5" customHeight="1">
+      <c r="A1" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="D1" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="E1" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="F1" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="G1" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="H1" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="I1" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="J1" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="L1" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="M1" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="25" t="s">
+    </row>
+    <row r="2" spans="1:13" ht="165">
+      <c r="A2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="I2" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="102">
-      <c r="A2" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" s="30"/>
-      <c r="M2" s="31"/>
-    </row>
-    <row r="3" spans="1:13" ht="165">
-      <c r="A3" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="F3" s="58" t="s">
-        <v>165</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="15" t="s">
-        <v>46</v>
+      <c r="J2" s="10"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" spans="1:13" ht="135">
+      <c r="A3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="J3" s="10"/>
-      <c r="K3" s="15" t="s">
-        <v>47</v>
-      </c>
+      <c r="K3" s="12"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
     </row>
-    <row r="4" spans="1:13" ht="135">
-      <c r="A4" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>161</v>
+    <row r="4" spans="1:13" ht="150">
+      <c r="A4" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>191</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>166</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="15"/>
+        <v>190</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>193</v>
+      </c>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
     </row>
-    <row r="5" spans="1:13" s="32" customFormat="1" ht="195">
-      <c r="A5" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F5" s="58" t="s">
+    <row r="5" spans="1:13" s="19" customFormat="1" ht="75">
+      <c r="A5" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="15"/>
+      <c r="I5" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J5" s="10"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="12"/>
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
     </row>
-    <row r="6" spans="1:13" s="32" customFormat="1" ht="75">
-      <c r="A6" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="B6" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="F6" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="15"/>
+    <row r="6" spans="1:13" s="19" customFormat="1" ht="90">
+      <c r="A6" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J6" s="10"/>
-      <c r="K6" s="15"/>
+      <c r="K6" s="12"/>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
     </row>
     <row r="7" spans="1:13" ht="90">
-      <c r="A7" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="15"/>
+      <c r="A7" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J7" s="10"/>
-      <c r="K7" s="15"/>
+      <c r="K7" s="12"/>
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
     </row>
-    <row r="8" spans="1:13" ht="90">
-      <c r="A8" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="58" t="s">
+    <row r="8" spans="1:13" ht="75">
+      <c r="A8" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="G8" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="15"/>
+      <c r="I8" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J8" s="10"/>
-      <c r="K8" s="15"/>
+      <c r="K8" s="12"/>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
     </row>
     <row r="9" spans="1:13" ht="75">
-      <c r="A9" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="57" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="15"/>
+      <c r="A9" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J9" s="10"/>
-      <c r="K9" s="15"/>
+      <c r="K9" s="12"/>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
     </row>
-    <row r="10" spans="1:13" ht="75">
-      <c r="A10" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B10" s="57" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="F10" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="H10" s="21"/>
-      <c r="I10" s="15"/>
+    <row r="10" spans="1:13" ht="90">
+      <c r="A10" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J10" s="10"/>
-      <c r="K10" s="15"/>
+      <c r="K10" s="12"/>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
     </row>
     <row r="11" spans="1:13" ht="90">
-      <c r="A11" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="B11" s="57" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="15"/>
+      <c r="A11" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J11" s="10"/>
-      <c r="K11" s="15"/>
+      <c r="K11" s="12"/>
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
     </row>
     <row r="12" spans="1:13" ht="90">
-      <c r="A12" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="F12" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="15"/>
+      <c r="A12" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J12" s="10"/>
-      <c r="K12" s="15"/>
+      <c r="K12" s="12"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
     </row>
     <row r="13" spans="1:13" ht="90">
-      <c r="A13" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="57" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="F13" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="15"/>
+      <c r="A13" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J13" s="10"/>
-      <c r="K13" s="15"/>
+      <c r="K13" s="12"/>
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
     </row>
-    <row r="14" spans="1:13" ht="90">
-      <c r="A14" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="57" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="F14" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="H14" s="21"/>
-      <c r="I14" s="15"/>
+    <row r="14" spans="1:13" ht="150">
+      <c r="A14" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J14" s="10"/>
-      <c r="K14" s="15"/>
+      <c r="K14" s="12"/>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
     </row>
-    <row r="15" spans="1:13" ht="150">
-      <c r="A15" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="B15" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="F15" s="71" t="s">
-        <v>171</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="15"/>
+    <row r="15" spans="1:13" ht="120">
+      <c r="A15" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="F15" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J15" s="10"/>
-      <c r="K15" s="15"/>
+      <c r="K15" s="12"/>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
     </row>
-    <row r="16" spans="1:13" ht="120">
-      <c r="A16" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B16" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="F16" s="71" t="s">
-        <v>171</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="15"/>
+    <row r="16" spans="1:13" ht="180">
+      <c r="A16" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J16" s="10"/>
-      <c r="K16" s="15"/>
+      <c r="K16" s="12"/>
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
     </row>
-    <row r="17" spans="1:13" ht="180">
-      <c r="A17" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B17" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="F17" s="71" t="s">
-        <v>171</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I2">
+    <cfRule type="containsText" dxfId="89" priority="91" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I2)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="92" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="87" priority="93" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="containsText" dxfId="86" priority="88" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K2)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="89" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="84" priority="90" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="80" priority="76" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="83" priority="85" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="77" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="86" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="78" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="81" priority="87" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3">
-    <cfRule type="containsText" dxfId="77" priority="73" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="80" priority="82" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="74" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="83" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="75" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="78" priority="84" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="74" priority="70" stopIfTrue="1" operator="containsText" text="Hold">
+  <conditionalFormatting sqref="I7">
+    <cfRule type="containsText" dxfId="77" priority="79" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I7)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="80" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="75" priority="81" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="containsText" dxfId="74" priority="76" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K7)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="77" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="72" priority="78" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8">
+    <cfRule type="containsText" dxfId="71" priority="73" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I8)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="74" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="69" priority="75" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8">
+    <cfRule type="containsText" dxfId="68" priority="70" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K8)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="71" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="66" priority="72" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9">
+    <cfRule type="containsText" dxfId="65" priority="67" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I9)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="68" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="63" priority="69" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K9">
+    <cfRule type="containsText" dxfId="62" priority="64" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K9)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="65" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="60" priority="66" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10">
+    <cfRule type="containsText" dxfId="59" priority="61" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I10)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="62" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="57" priority="63" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I10)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K10">
+    <cfRule type="containsText" dxfId="56" priority="58" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K10)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="59" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="60" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K10)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11">
+    <cfRule type="containsText" dxfId="53" priority="55" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I11)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="56" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="51" priority="57" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="containsText" dxfId="50" priority="52" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K11)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="53" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="48" priority="54" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12">
+    <cfRule type="containsText" dxfId="47" priority="49" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I12)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="50" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="45" priority="51" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="containsText" dxfId="44" priority="46" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K12)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="47" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="42" priority="48" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
+    <cfRule type="containsText" dxfId="41" priority="43" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I13)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="44" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="39" priority="45" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="containsText" dxfId="38" priority="40" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K13)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="41" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="42" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K14">
+    <cfRule type="containsText" dxfId="35" priority="34" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K14)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="35" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="36" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K14)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
+    <cfRule type="containsText" dxfId="32" priority="22" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K16)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="23" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="24" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K15">
+    <cfRule type="containsText" dxfId="29" priority="28" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K15)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="29" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="27" priority="30" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K15)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:I6">
+    <cfRule type="containsText" dxfId="26" priority="19" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I4)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="71" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="20" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="72" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="24" priority="21" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K6">
+    <cfRule type="containsText" dxfId="23" priority="16" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",K5)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="17" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="18" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",K5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I14">
+    <cfRule type="containsText" dxfId="20" priority="13" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I14)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="14" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="15" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I14)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16">
+    <cfRule type="containsText" dxfId="17" priority="7" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I16)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="8" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="9" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
+    <cfRule type="containsText" dxfId="14" priority="4" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",I15)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="5" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="6" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",I15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="containsText" dxfId="71" priority="67" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="5" priority="1" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K4)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="68" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="69" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="68" priority="64" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I8)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="65" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="66" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K8">
-    <cfRule type="containsText" dxfId="65" priority="61" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K8)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="62" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="63" priority="63" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I9">
-    <cfRule type="containsText" dxfId="62" priority="58" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I9)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="59" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="60" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K9">
-    <cfRule type="containsText" dxfId="59" priority="55" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K9)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="56" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="57" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I10">
-    <cfRule type="containsText" dxfId="56" priority="52" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I10)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="53" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="54" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I10)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K10">
-    <cfRule type="containsText" dxfId="53" priority="49" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K10)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="50" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="51" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K10)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11">
-    <cfRule type="containsText" dxfId="50" priority="46" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I11)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="47" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="48" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11">
-    <cfRule type="containsText" dxfId="47" priority="43" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K11)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="44" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="45" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="44" priority="40" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I12)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="41" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="42" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="41" priority="37" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K12)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="38" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="39" priority="39" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="38" priority="34" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I13)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="35" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="36" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="35" priority="31" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K13)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="32" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="33" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="32" priority="28" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I14)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="29" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="30" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="29" priority="25" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K14)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="26" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="27" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="26" priority="22" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I15)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="23" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="24" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I15)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="23" priority="19" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K15)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="20" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="21" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K15)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I16">
-    <cfRule type="containsText" dxfId="20" priority="16" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I16)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="17" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="18" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I16)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="17" priority="13" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K16)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="14" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="15" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K16)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
-    <cfRule type="containsText" dxfId="14" priority="10" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I17)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="11" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="12" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I17)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K17">
-    <cfRule type="containsText" dxfId="11" priority="7" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K17)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="9" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K17)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I7">
-    <cfRule type="containsText" dxfId="8" priority="4" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",I5)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="5" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",I5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K7">
-    <cfRule type="containsText" dxfId="5" priority="1" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",K5)))</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="4" priority="2" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="3" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",K5)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Passed",K4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K17 I3:I17" xr:uid="{CE5CDE44-95E3-4A5E-BC40-8AA37EE8C6A6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I16 K2:K16" xr:uid="{CE5CDE44-95E3-4A5E-BC40-8AA37EE8C6A6}">
       <formula1>"Passed,Failed,Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3605,84 +3565,63 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.42578125" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="A1" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.95" customHeight="1">
+      <c r="A2" s="59" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="69.95" customHeight="1">
-      <c r="A2" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>59</v>
+      <c r="E2" s="62" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="37"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="37" t="s">
-        <v>64</v>
-      </c>
+      <c r="A3" s="23"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="37"/>
+      <c r="A5" s="23"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{BBC4ADAF-9AA4-4E41-9B9B-912A2FA6B002}"/>
-    <hyperlink ref="E4" r:id="rId2" xr:uid="{E6A00837-947B-4D94-A06C-D6ADF3262683}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3690,11 +3629,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C7F3CB5-277D-435E-8C56-2266F39E61EA}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" customWidth="1"/>
     <col min="4" max="4" width="34.140625" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" customWidth="1"/>
@@ -3702,212 +3641,307 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>70</v>
+      <c r="A1" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="54" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="59" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="59" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>73</v>
+      <c r="A2" s="63" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>55</v>
+      <c r="A3" s="64"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="61"/>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>73</v>
+      <c r="A5" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>73</v>
+      <c r="A7" s="65"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="10"/>
+      <c r="A8" s="63" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>60</v>
+      <c r="A9" s="64"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="10"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="10"/>
+      <c r="A11" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="10"/>
+      <c r="A12" s="64"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="10"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="10"/>
+      <c r="A14" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="64"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="65"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
+  <mergeCells count="15">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="A8:A10"/>
   </mergeCells>
-  <conditionalFormatting sqref="E2:E5">
-    <cfRule type="containsText" dxfId="2" priority="1" stopIfTrue="1" operator="containsText" text="Hold">
+  <conditionalFormatting sqref="E2">
+    <cfRule type="containsText" dxfId="11" priority="7" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",E2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="8" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="9" priority="9" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E16">
+    <cfRule type="containsText" dxfId="8" priority="1" stopIfTrue="1" operator="containsText" text="Hold">
+      <formula>NOT(ISERROR(SEARCH("Hold",E3)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="3" stopIfTrue="1" operator="containsText" text="Passed">
+      <formula>NOT(ISERROR(SEARCH("Passed",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E5" xr:uid="{BA0D1261-EDCC-4BE5-A420-A41FD9E77970}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E16" xr:uid="{B8279905-6E8C-45B3-A181-F95AB56885C0}">
       <formula1>"Passed,Failed,Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3917,115 +3951,88 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4724C62D-BB28-468D-A25F-C910E07B66CE}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.5">
-      <c r="A1" s="62" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
+      <c r="A1" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>97</v>
+      <c r="A2" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="61" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="61" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="19" t="s">
-        <v>98</v>
+      <c r="A3" s="16" t="s">
+        <v>198</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="12">
-        <v>2</v>
-      </c>
-      <c r="D3" s="12">
-        <v>2</v>
-      </c>
-      <c r="E3" s="12">
-        <v>0</v>
-      </c>
-      <c r="F3" s="12">
-        <v>2</v>
-      </c>
-      <c r="G3" s="17">
+        <v>53</v>
+      </c>
+      <c r="C3" s="11">
+        <v>15</v>
+      </c>
+      <c r="D3" s="11">
+        <v>14</v>
+      </c>
+      <c r="E3" s="11">
         <v>1</v>
       </c>
-      <c r="H3" s="17">
-        <v>0</v>
-      </c>
-      <c r="I3" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="19"/>
-      <c r="B4" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="12">
-        <v>2</v>
-      </c>
-      <c r="D4" s="12">
-        <v>2</v>
-      </c>
-      <c r="E4" s="12">
-        <v>0</v>
-      </c>
-      <c r="F4" s="12">
-        <v>2</v>
-      </c>
-      <c r="G4" s="17">
-        <v>1</v>
-      </c>
-      <c r="H4" s="17">
-        <v>0</v>
-      </c>
-      <c r="I4" s="18">
+      <c r="F3" s="11">
+        <v>15</v>
+      </c>
+      <c r="G3" s="14">
+        <v>0.93330000000000002</v>
+      </c>
+      <c r="H3" s="14">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="I3" s="15">
         <v>1</v>
       </c>
     </row>

--- a/Day1/BiswayanNath_ManualTesting.xlsx
+++ b/Day1/BiswayanNath_ManualTesting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\biswa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEED953-F5B3-4ED3-ADBD-4847A235564D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2246D1-0846-4C50-BCB2-79EFB9BEF69B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -381,260 +381,292 @@
     <t>TC_MakeMyTrip_05</t>
   </si>
   <si>
-    <t>1. Chennai
+    <t>To verify clicking “Visa Free Packages” displays predefined destinations list.</t>
+  </si>
+  <si>
+    <t>To verify clicking a destination loads relevant holiday packages.</t>
+  </si>
+  <si>
+    <t>1. Verify clicking “Visa Free Packages” displays predefined destinations list.
+2. Verify clicking a destination loads relevant holiday packages.
+3. Verify UI content (images, labels) loads correctly.</t>
+  </si>
+  <si>
+    <t>1. Click on Visa Free Packages.</t>
+  </si>
+  <si>
+    <t>1. Click on Visa Free Packages.
+2. Click on the first destination.
+3. Click on the first package.</t>
+  </si>
+  <si>
+    <t>It should open a trip package with specified details.</t>
+  </si>
+  <si>
+    <t>It should not accept the specified details.</t>
+  </si>
+  <si>
+    <t>It should display a list of predefined destinations.</t>
+  </si>
+  <si>
+    <t>To verify UI content (images, labels) loads correctly.</t>
+  </si>
+  <si>
+    <t>It should display images and labels of the selected location.</t>
+  </si>
+  <si>
+    <t>Verify clicking “Disney Cruise” displays cruise categories</t>
+  </si>
+  <si>
+    <t>1. Verify clicking “Disney Cruise” displays cruise categories
+2. Verify “View All” navigates to full Disney Cruise listing page.
+3. Verify clicking a cruise duration loads correct package listings.</t>
+  </si>
+  <si>
+    <t>To verify clicking “Disney Cruise” displays cruise categories.</t>
+  </si>
+  <si>
+    <t>1. Click on Disney Cruise.</t>
+  </si>
+  <si>
+    <t>It should display a list of cruise categories.</t>
+  </si>
+  <si>
+    <t>To verify “View All” navigates to full Disney Cruise listing page.</t>
+  </si>
+  <si>
+    <t>It should display the list of all available cruise trips.</t>
+  </si>
+  <si>
+    <t>To verify clicking a cruise duration loads correct package listings.</t>
+  </si>
+  <si>
+    <t>1. Click on Disney Cruise.
+2. Click on View All.</t>
+  </si>
+  <si>
+    <t>It should open a Disney cruise package with required details.</t>
+  </si>
+  <si>
+    <t>To verify packages shown are actually within “last-minute” time window.</t>
+  </si>
+  <si>
+    <t>1. Click on Disney Cruise.
+2. Click on View All.
+3. Click on the first package.</t>
+  </si>
+  <si>
+    <t>1. Click on Last Minute Deals.
+2. Click on View All.
+3. Click on the first package.</t>
+  </si>
+  <si>
+    <t>To verify expired deals are not displayed.</t>
+  </si>
+  <si>
+    <t>It should open a Last Minute Deal which starts within 3 months from current date.</t>
+  </si>
+  <si>
+    <t>The start date of the trip should be after the current date.</t>
+  </si>
+  <si>
+    <t>It should display images and labels of the selected package.</t>
+  </si>
+  <si>
+    <t>To verify recently viewed packages section displays after user interaction.</t>
+  </si>
+  <si>
+    <t>Verify “Review &amp; Pay / Book Now” CTA works correctly</t>
+  </si>
+  <si>
+    <t>To verify “Review &amp; Pay / Book Now” CTA works correctly.</t>
+  </si>
+  <si>
+    <t>1. Navigate to any package details page.
+2. Navigate to Holiday Packages page, and click on the first package in the Recently Viewed Packages section.</t>
+  </si>
+  <si>
+    <t>1. Navigate to any package details page, and click on Proceed to Payment.
+2. Navigate to Holiday Packages page, and click on the first package in the Recently Viewed Packages section.</t>
+  </si>
+  <si>
+    <t>It should open the package details of the last seen package.</t>
+  </si>
+  <si>
+    <t>It should open the review package page for the last seen package.</t>
+  </si>
+  <si>
+    <t>Completion Percentage</t>
+  </si>
+  <si>
+    <t>TS_MakeMyTrip_01</t>
+  </si>
+  <si>
+    <t>TR_MakeMyTrip_01</t>
+  </si>
+  <si>
+    <t>BR_MakeMyTrip_01</t>
+  </si>
+  <si>
+    <t>BR_MakeMyTrip_02</t>
+  </si>
+  <si>
+    <t>BR_MakeMyTrip_03</t>
+  </si>
+  <si>
+    <t>BR_MakeMyTrip_04</t>
+  </si>
+  <si>
+    <t>BR_MakeMyTrip_05</t>
+  </si>
+  <si>
+    <t>TR_MakeMyTrip_02</t>
+  </si>
+  <si>
+    <t>TR_MakeMyTrip_03</t>
+  </si>
+  <si>
+    <t>TR_MakeMyTrip_04</t>
+  </si>
+  <si>
+    <t>TR_MakeMyTrip_05</t>
+  </si>
+  <si>
+    <t>TS_MakeMyTrip_02</t>
+  </si>
+  <si>
+    <t>TS_MakeMyTrip_03</t>
+  </si>
+  <si>
+    <t>TS_MakeMyTrip_04</t>
+  </si>
+  <si>
+    <t>TS_MakeMyTrip_05</t>
+  </si>
+  <si>
+    <t>It opens a trip package with specified details.</t>
+  </si>
+  <si>
+    <t>It displays a list of predefined destinations.</t>
+  </si>
+  <si>
+    <t>It displays details of a Visa Free Holiday package.</t>
+  </si>
+  <si>
+    <t>It should display details of a Visa Free Holiday package.</t>
+  </si>
+  <si>
+    <t>It displays images and labels of the selected location.</t>
+  </si>
+  <si>
+    <t>It displays a list of cruise categories.</t>
+  </si>
+  <si>
+    <t>It displays the list of all available cruise trips.</t>
+  </si>
+  <si>
+    <t>It opens a Disney Cruise with specified details.</t>
+  </si>
+  <si>
+    <t>It opens a Last Minute Deal which starts 27 days from current date.</t>
+  </si>
+  <si>
+    <t>It opens a Last Minute Deal which starts after the current date.</t>
+  </si>
+  <si>
+    <t>It displays images and labels of the selected package correctly.</t>
+  </si>
+  <si>
+    <t>It opens the package details of the last seen package.</t>
+  </si>
+  <si>
+    <t>It opens the package details of the last seen package for the specified destination.</t>
+  </si>
+  <si>
+    <t>It should open the package details of the last seen package for the specified destination.</t>
+  </si>
+  <si>
+    <t>To verify packages are grouped with destination filters.</t>
+  </si>
+  <si>
+    <t>1. Click on the first destination filter in the Recently Viewed Packages section.
+2. Click on the first package from the list.</t>
+  </si>
+  <si>
+    <t>1. Verify recently viewed packages section displays after user interaction.
+2. Verify packages are grouped with destination filters.
+3. Verify “Review &amp; Pay / Book Now” CTA works correctly</t>
+  </si>
+  <si>
+    <t>Verify packages are grouped with destination filters</t>
+  </si>
+  <si>
+    <t>It opens the review package page for the last seen package.</t>
+  </si>
+  <si>
+    <t>Actual Result Iteration 2</t>
+  </si>
+  <si>
+    <t>Status
+ Iteration 2</t>
+  </si>
+  <si>
+    <t>Verify multiple filters are being applied correctly</t>
+  </si>
+  <si>
+    <t>1. Verify search with valid input data.
+2. Verify search with invalid input data.
+3. Verify multiple filters are being applied correctly.</t>
+  </si>
+  <si>
+    <t>To verify multiple filters are being applied correctly</t>
+  </si>
+  <si>
+    <t>1. Enter source location, departure date and number of rooms and guests.
+2. Enter all the filters.
+3. Click on search button.</t>
+  </si>
+  <si>
+    <t>It should open all trip packages with the specified details.</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>The trip packages displayed are not within the specified price range.</t>
+  </si>
+  <si>
+    <t>DF_HolidayPackage_01</t>
+  </si>
+  <si>
+    <t>Multiple filters applied do not enforce price range correctly.</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Make My Trip Application</t>
+  </si>
+  <si>
+    <t>It does not accept the invalid data (destination location) and replaces it with default location.</t>
+  </si>
+  <si>
+    <t>abc@gmail.com</t>
+  </si>
+  <si>
+    <t>1. Kolkata
 2. Kerala
 3. 12 May 2026
 4. 2 Adults, 1 Room</t>
   </si>
   <si>
-    <t>To verify clicking “Visa Free Packages” displays predefined destinations list.</t>
-  </si>
-  <si>
-    <t>To verify clicking a destination loads relevant holiday packages.</t>
-  </si>
-  <si>
-    <t>1. Verify clicking “Visa Free Packages” displays predefined destinations list.
-2. Verify clicking a destination loads relevant holiday packages.
-3. Verify UI content (images, labels) loads correctly.</t>
-  </si>
-  <si>
-    <t>1. Click on Visa Free Packages.</t>
-  </si>
-  <si>
-    <t>1. Click on Visa Free Packages.
-2. Click on the first destination.
-3. Click on the first package.</t>
-  </si>
-  <si>
-    <t>It should open a trip package with specified details.</t>
-  </si>
-  <si>
-    <t>It should not accept the specified details.</t>
-  </si>
-  <si>
-    <t>It should display a list of predefined destinations.</t>
-  </si>
-  <si>
-    <t>To verify UI content (images, labels) loads correctly.</t>
-  </si>
-  <si>
-    <t>It should display images and labels of the selected location.</t>
-  </si>
-  <si>
-    <t>Verify clicking “Disney Cruise” displays cruise categories</t>
-  </si>
-  <si>
-    <t>1. Verify clicking “Disney Cruise” displays cruise categories
-2. Verify “View All” navigates to full Disney Cruise listing page.
-3. Verify clicking a cruise duration loads correct package listings.</t>
-  </si>
-  <si>
-    <t>To verify clicking “Disney Cruise” displays cruise categories.</t>
-  </si>
-  <si>
-    <t>1. Click on Disney Cruise.</t>
-  </si>
-  <si>
-    <t>It should display a list of cruise categories.</t>
-  </si>
-  <si>
-    <t>To verify “View All” navigates to full Disney Cruise listing page.</t>
-  </si>
-  <si>
-    <t>It should display the list of all available cruise trips.</t>
-  </si>
-  <si>
-    <t>To verify clicking a cruise duration loads correct package listings.</t>
-  </si>
-  <si>
-    <t>1. Click on Disney Cruise.
-2. Click on View All.</t>
-  </si>
-  <si>
-    <t>It should open a Disney cruise package with required details.</t>
-  </si>
-  <si>
-    <t>To verify packages shown are actually within “last-minute” time window.</t>
-  </si>
-  <si>
-    <t>1. Click on Disney Cruise.
-2. Click on View All.
-3. Click on the first package.</t>
-  </si>
-  <si>
-    <t>1. Click on Last Minute Deals.
-2. Click on View All.
-3. Click on the first package.</t>
-  </si>
-  <si>
-    <t>To verify expired deals are not displayed.</t>
-  </si>
-  <si>
-    <t>It should open a Last Minute Deal which starts within 3 months from current date.</t>
-  </si>
-  <si>
-    <t>The start date of the trip should be after the current date.</t>
-  </si>
-  <si>
-    <t>It should display images and labels of the selected package.</t>
-  </si>
-  <si>
-    <t>To verify recently viewed packages section displays after user interaction.</t>
-  </si>
-  <si>
-    <t>Verify “Review &amp; Pay / Book Now” CTA works correctly</t>
-  </si>
-  <si>
-    <t>To verify “Review &amp; Pay / Book Now” CTA works correctly.</t>
-  </si>
-  <si>
-    <t>1. Navigate to any package details page.
-2. Navigate to Holiday Packages page, and click on the first package in the Recently Viewed Packages section.</t>
-  </si>
-  <si>
-    <t>1. Navigate to any package details page, and click on Proceed to Payment.
-2. Navigate to Holiday Packages page, and click on the first package in the Recently Viewed Packages section.</t>
-  </si>
-  <si>
-    <t>It should open the package details of the last seen package.</t>
-  </si>
-  <si>
-    <t>It should open the review package page for the last seen package.</t>
-  </si>
-  <si>
-    <t>1. Chennai
+    <t>1. Kolkata
 2. iaooxoias
 3. 12 May 2026
 4. 2 Adults, 1 Room</t>
   </si>
   <si>
-    <t>Completion Percentage</t>
-  </si>
-  <si>
-    <t>TS_MakeMyTrip_01</t>
-  </si>
-  <si>
-    <t>TR_MakeMyTrip_01</t>
-  </si>
-  <si>
-    <t>BR_MakeMyTrip_01</t>
-  </si>
-  <si>
-    <t>BR_MakeMyTrip_02</t>
-  </si>
-  <si>
-    <t>BR_MakeMyTrip_03</t>
-  </si>
-  <si>
-    <t>BR_MakeMyTrip_04</t>
-  </si>
-  <si>
-    <t>BR_MakeMyTrip_05</t>
-  </si>
-  <si>
-    <t>TR_MakeMyTrip_02</t>
-  </si>
-  <si>
-    <t>TR_MakeMyTrip_03</t>
-  </si>
-  <si>
-    <t>TR_MakeMyTrip_04</t>
-  </si>
-  <si>
-    <t>TR_MakeMyTrip_05</t>
-  </si>
-  <si>
-    <t>TS_MakeMyTrip_02</t>
-  </si>
-  <si>
-    <t>TS_MakeMyTrip_03</t>
-  </si>
-  <si>
-    <t>TS_MakeMyTrip_04</t>
-  </si>
-  <si>
-    <t>TS_MakeMyTrip_05</t>
-  </si>
-  <si>
-    <t>It opens a trip package with specified details.</t>
-  </si>
-  <si>
-    <t>It displays a list of predefined destinations.</t>
-  </si>
-  <si>
-    <t>It displays details of a Visa Free Holiday package.</t>
-  </si>
-  <si>
-    <t>It should display details of a Visa Free Holiday package.</t>
-  </si>
-  <si>
-    <t>It displays images and labels of the selected location.</t>
-  </si>
-  <si>
-    <t>It displays a list of cruise categories.</t>
-  </si>
-  <si>
-    <t>It displays the list of all available cruise trips.</t>
-  </si>
-  <si>
-    <t>It opens a Disney Cruise with specified details.</t>
-  </si>
-  <si>
-    <t>It opens a Last Minute Deal which starts 27 days from current date.</t>
-  </si>
-  <si>
-    <t>It opens a Last Minute Deal which starts after the current date.</t>
-  </si>
-  <si>
-    <t>It displays images and labels of the selected package correctly.</t>
-  </si>
-  <si>
-    <t>It opens the package details of the last seen package.</t>
-  </si>
-  <si>
-    <t>It opens the package details of the last seen package for the specified destination.</t>
-  </si>
-  <si>
-    <t>It should open the package details of the last seen package for the specified destination.</t>
-  </si>
-  <si>
-    <t>To verify packages are grouped with destination filters.</t>
-  </si>
-  <si>
-    <t>1. Click on the first destination filter in the Recently Viewed Packages section.
-2. Click on the first package from the list.</t>
-  </si>
-  <si>
-    <t>1. Verify recently viewed packages section displays after user interaction.
-2. Verify packages are grouped with destination filters.
-3. Verify “Review &amp; Pay / Book Now” CTA works correctly</t>
-  </si>
-  <si>
-    <t>Verify packages are grouped with destination filters</t>
-  </si>
-  <si>
-    <t>It opens the review package page for the last seen package.</t>
-  </si>
-  <si>
-    <t>Actual Result Iteration 2</t>
-  </si>
-  <si>
-    <t>Status
- Iteration 2</t>
-  </si>
-  <si>
-    <t>Verify multiple filters are being applied correctly</t>
-  </si>
-  <si>
-    <t>1. Verify search with valid input data.
-2. Verify search with invalid input data.
-3. Verify multiple filters are being applied correctly.</t>
-  </si>
-  <si>
-    <t>To verify multiple filters are being applied correctly</t>
-  </si>
-  <si>
-    <t>1. Chennai
+    <t>1. Kolkata
 2. Kerala
 3. 12 May 2026
 4. 2 Adults, 1 Room
@@ -643,63 +675,17 @@
     ii. ₹0 - ₹20000
     iii. 5 Star</t>
   </si>
-  <si>
-    <t>1. Enter source location, departure date and number of rooms and guests.
-2. Enter all the filters.
-3. Click on search button.</t>
-  </si>
-  <si>
-    <t>It should open all trip packages with the specified details.</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>The trip packages displayed are not within the specified price range.</t>
-  </si>
-  <si>
-    <t>DF_HolidayPackage_01</t>
-  </si>
-  <si>
-    <t>Multiple filters applied do not enforce price range correctly.</t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
-    <t>Make My Trip Application</t>
-  </si>
-  <si>
-    <t>It does not accept the invalid data (destination location) and replaces it with default location.</t>
-  </si>
-  <si>
-    <t>abc@gmail.com</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1108,41 +1094,41 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1158,73 +1144,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1233,64 +1216,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1298,28 +1278,7 @@
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="90">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="87">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2233,7 +2192,7 @@
       <c r="B2" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="42" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2244,7 +2203,7 @@
       <c r="B3" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="43" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2255,7 +2214,7 @@
       <c r="B4" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="44" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2266,7 +2225,7 @@
       <c r="B5" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="44" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2275,9 +2234,9 @@
         <v>57</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2288,7 +2247,7 @@
       <c r="B7" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="43" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2299,7 +2258,7 @@
       <c r="B8" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="44" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2310,7 +2269,7 @@
       <c r="B9" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="44" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2321,7 +2280,7 @@
       <c r="B10" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="45" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2332,7 +2291,7 @@
       <c r="B11" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="43" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2341,9 +2300,9 @@
         <v>5</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="44" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2354,7 +2313,7 @@
       <c r="B13" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="44" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2365,7 +2324,7 @@
       <c r="B14" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="45" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2376,7 +2335,7 @@
       <c r="B15" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="43" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2387,7 +2346,7 @@
       <c r="B16" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="44" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2398,7 +2357,7 @@
       <c r="B17" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C17" s="44" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2409,7 +2368,7 @@
       <c r="B18" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="45" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2420,7 +2379,7 @@
       <c r="B19" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="46" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2431,7 +2390,7 @@
       <c r="B20" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="47" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2440,9 +2399,9 @@
         <v>6</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="C21" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="47" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2451,9 +2410,9 @@
         <v>57</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="48" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2533,7 +2492,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="19" customFormat="1" ht="51">
@@ -2553,7 +2512,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="19" customFormat="1" ht="51">
@@ -2573,7 +2532,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="19" customFormat="1" ht="51">
@@ -2613,7 +2572,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="19" customFormat="1">
@@ -2714,43 +2673,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="40.5" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="53" t="s">
+      <c r="F1" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="57" t="s">
-        <v>185</v>
-      </c>
-      <c r="K1" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="L1" s="53" t="s">
+      <c r="J1" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="K1" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="L1" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="53" t="s">
+      <c r="M1" s="51" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2770,14 +2729,14 @@
       <c r="E2" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="42" t="s">
-        <v>114</v>
+      <c r="F2" s="65" t="s">
+        <v>198</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>30</v>
@@ -2803,14 +2762,14 @@
       <c r="E3" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="F3" s="50" t="s">
-        <v>149</v>
+      <c r="F3" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>30</v>
@@ -2831,28 +2790,28 @@
         <v>109</v>
       </c>
       <c r="D4" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="G4" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="H4" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="I4" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>193</v>
-      </c>
       <c r="J4" s="17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
@@ -2868,19 +2827,19 @@
         <v>109</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="53" t="s">
         <v>43</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>30</v>
@@ -2901,19 +2860,19 @@
         <v>109</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="F6" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="53" t="s">
         <v>43</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>30</v>
@@ -2934,19 +2893,19 @@
         <v>109</v>
       </c>
       <c r="D7" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>124</v>
-      </c>
       <c r="H7" s="17" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>30</v>
@@ -2967,19 +2926,19 @@
         <v>109</v>
       </c>
       <c r="D8" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="F8" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F8" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>129</v>
-      </c>
       <c r="H8" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>30</v>
@@ -3000,19 +2959,19 @@
         <v>109</v>
       </c>
       <c r="D9" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>131</v>
-      </c>
       <c r="H9" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>30</v>
@@ -3033,19 +2992,19 @@
         <v>109</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F10" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="F10" s="53" t="s">
         <v>43</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>30</v>
@@ -3066,19 +3025,19 @@
         <v>109</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="F11" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="53" t="s">
         <v>43</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>30</v>
@@ -3099,19 +3058,19 @@
         <v>109</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="F12" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" s="53" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>30</v>
@@ -3132,19 +3091,19 @@
         <v>109</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="53" t="s">
         <v>43</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>30</v>
@@ -3165,19 +3124,19 @@
         <v>109</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="F14" s="55" t="s">
+        <v>144</v>
+      </c>
+      <c r="F14" s="53" t="s">
         <v>43</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>30</v>
@@ -3198,19 +3157,19 @@
         <v>109</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="F15" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="F15" s="53" t="s">
         <v>43</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>30</v>
@@ -3231,19 +3190,19 @@
         <v>109</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="F16" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="F16" s="53" t="s">
         <v>43</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>30</v>
@@ -3255,299 +3214,299 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="89" priority="91" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="86" priority="91" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="92" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="92" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="87" priority="93" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="84" priority="93" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2">
-    <cfRule type="containsText" dxfId="86" priority="88" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="83" priority="88" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="89" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="89" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="90" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="81" priority="90" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="83" priority="85" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="80" priority="85" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="86" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="86" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="87" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="78" priority="87" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3">
-    <cfRule type="containsText" dxfId="80" priority="82" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="77" priority="82" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="83" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="83" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="84" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="75" priority="84" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="77" priority="79" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="74" priority="79" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I7)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="80" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="80" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="81" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="72" priority="81" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="74" priority="76" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="71" priority="76" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K7)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="77" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="77" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="78" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="69" priority="78" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="71" priority="73" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="68" priority="73" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I8)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="74" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="74" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="75" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="66" priority="75" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8">
-    <cfRule type="containsText" dxfId="68" priority="70" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="65" priority="70" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K8)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="71" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="71" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="72" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="63" priority="72" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9">
-    <cfRule type="containsText" dxfId="65" priority="67" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="62" priority="67" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I9)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="68" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="68" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="63" priority="69" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="60" priority="69" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9">
-    <cfRule type="containsText" dxfId="62" priority="64" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="59" priority="64" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K9)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="65" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="65" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="66" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="57" priority="66" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10">
-    <cfRule type="containsText" dxfId="59" priority="61" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="56" priority="61" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I10)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="62" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="62" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="63" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="54" priority="63" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10">
-    <cfRule type="containsText" dxfId="56" priority="58" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="53" priority="58" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K10)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="59" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="59" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="60" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="51" priority="60" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11">
-    <cfRule type="containsText" dxfId="53" priority="55" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="50" priority="55" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I11)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="56" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="56" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="57" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="48" priority="57" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="containsText" dxfId="50" priority="52" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="47" priority="52" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K11)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="53" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="53" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="54" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="45" priority="54" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="47" priority="49" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="44" priority="49" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I12)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="50" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="50" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="51" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="42" priority="51" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="44" priority="46" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="41" priority="46" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K12)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="47" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="47" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="48" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="39" priority="48" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="41" priority="43" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="38" priority="43" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I13)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="44" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="44" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="39" priority="45" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="36" priority="45" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="38" priority="40" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="35" priority="40" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K13)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="41" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="41" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="42" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="33" priority="42" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="35" priority="34" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="32" priority="34" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K14)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="35" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="35" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="36" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="30" priority="36" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="32" priority="22" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="29" priority="22" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K16)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="23" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="23" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="24" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="27" priority="24" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="29" priority="28" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="26" priority="28" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K15)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="29" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="29" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="30" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="24" priority="30" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I6">
-    <cfRule type="containsText" dxfId="26" priority="19" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="23" priority="19" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I4)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="20" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="20" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="21" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="21" priority="21" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K6">
-    <cfRule type="containsText" dxfId="23" priority="16" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="20" priority="16" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K5)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="17" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="17" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="18" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="18" priority="18" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14">
-    <cfRule type="containsText" dxfId="20" priority="13" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="17" priority="13" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I14)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="14" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="14" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="15" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="15" priority="15" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16">
-    <cfRule type="containsText" dxfId="17" priority="7" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="14" priority="7" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I16)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="8" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="8" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="9" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="12" priority="9" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="14" priority="4" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="11" priority="4" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",I15)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="5" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="5" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="6" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="9" priority="6" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",I15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="containsText" dxfId="5" priority="1" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="8" priority="1" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K4)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="6" priority="3" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",K4)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3574,43 +3533,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="56" t="s">
+      <c r="C1" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="54" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="69.95" customHeight="1">
-      <c r="A2" s="59" t="s">
-        <v>195</v>
-      </c>
-      <c r="B2" s="59" t="s">
+      <c r="A2" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="60" t="s">
-        <v>196</v>
-      </c>
-      <c r="D2" s="59" t="s">
+      <c r="C2" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="62" t="s">
-        <v>200</v>
-      </c>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="59" t="s">
         <v>197</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3641,34 +3600,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="52" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="B2" s="63" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="63" t="s">
+      <c r="A2" s="60" t="s">
         <v>151</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>149</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>89</v>
@@ -3681,9 +3640,9 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="64"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
       <c r="D3" s="11" t="s">
         <v>90</v>
       </c>
@@ -3695,28 +3654,28 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="65"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
       <c r="D4" s="11" t="s">
         <v>102</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="B5" s="63" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="63" t="s">
-        <v>162</v>
+      <c r="A5" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>160</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>112</v>
@@ -3729,9 +3688,9 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="64"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
       <c r="D6" s="11" t="s">
         <v>113</v>
       </c>
@@ -3743,9 +3702,9 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="65"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
+      <c r="A7" s="62"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
       <c r="D7" s="11" t="s">
         <v>91</v>
       </c>
@@ -3757,14 +3716,14 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="63" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="63" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>163</v>
+      <c r="A8" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>161</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>92</v>
@@ -3777,9 +3736,9 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="64"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
       <c r="D9" s="11" t="s">
         <v>93</v>
       </c>
@@ -3791,9 +3750,9 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="65"/>
-      <c r="B10" s="65"/>
-      <c r="C10" s="65"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
       <c r="D10" s="11" t="s">
         <v>94</v>
       </c>
@@ -3805,14 +3764,14 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="63" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" s="63" t="s">
-        <v>164</v>
+      <c r="A11" s="60" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>162</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>95</v>
@@ -3825,9 +3784,9 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="64"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
       <c r="D12" s="11" t="s">
         <v>96</v>
       </c>
@@ -3839,9 +3798,9 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="65"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="65"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
       <c r="D13" s="11" t="s">
         <v>97</v>
       </c>
@@ -3853,14 +3812,14 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="B14" s="63" t="s">
-        <v>161</v>
-      </c>
-      <c r="C14" s="63" t="s">
-        <v>165</v>
+      <c r="A14" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>163</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>98</v>
@@ -3873,9 +3832,9 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="64"/>
-      <c r="B15" s="64"/>
-      <c r="C15" s="64"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
       <c r="D15" s="11" t="s">
         <v>99</v>
       </c>
@@ -3887,9 +3846,9 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="65"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="65"/>
+      <c r="A16" s="62"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="11" t="s">
         <v>100</v>
       </c>
@@ -3919,24 +3878,24 @@
     <mergeCell ref="A8:A10"/>
   </mergeCells>
   <conditionalFormatting sqref="E2">
-    <cfRule type="containsText" dxfId="11" priority="7" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="5" priority="7" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",E2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="9" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="3" priority="9" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E16">
-    <cfRule type="containsText" dxfId="8" priority="1" stopIfTrue="1" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="2" priority="1" stopIfTrue="1" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",E3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="3" stopIfTrue="1" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="0" priority="3" stopIfTrue="1" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3966,50 +3925,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.5">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="61" t="s">
+      <c r="H2" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="61" t="s">
-        <v>150</v>
+      <c r="I2" s="58" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="16" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>53</v>

--- a/Day1/BiswayanNath_ManualTesting.xlsx
+++ b/Day1/BiswayanNath_ManualTesting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\biswa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2246D1-0846-4C50-BCB2-79EFB9BEF69B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C578829D-D683-4E2C-976D-6B03242CB770}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="201">
   <si>
     <t>Issue Type</t>
   </si>
@@ -680,12 +680,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1094,41 +1101,41 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1144,70 +1151,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1216,44 +1223,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1263,14 +1273,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2669,7 +2679,7 @@
     <col min="10" max="10" width="23.85546875" customWidth="1"/>
     <col min="11" max="11" width="16.140625" customWidth="1"/>
     <col min="12" max="12" width="9.85546875" customWidth="1"/>
-    <col min="13" max="13" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="40.5" customHeight="1">
@@ -2729,7 +2739,7 @@
       <c r="E2" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="60" t="s">
         <v>198</v>
       </c>
       <c r="G2" s="17" t="s">
@@ -2744,7 +2754,9 @@
       <c r="J2" s="10"/>
       <c r="K2" s="12"/>
       <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="M2" s="66" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="3" spans="1:13" ht="135">
       <c r="A3" s="11" t="s">
@@ -2762,7 +2774,7 @@
       <c r="E3" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="F3" s="65" t="s">
+      <c r="F3" s="60" t="s">
         <v>199</v>
       </c>
       <c r="G3" s="17" t="s">
@@ -2777,7 +2789,9 @@
       <c r="J3" s="10"/>
       <c r="K3" s="12"/>
       <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="M3" s="66" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="150">
       <c r="A4" s="11" t="s">
@@ -2795,7 +2809,7 @@
       <c r="E4" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="F4" s="65" t="s">
+      <c r="F4" s="60" t="s">
         <v>200</v>
       </c>
       <c r="G4" s="17" t="s">
@@ -2814,7 +2828,9 @@
         <v>190</v>
       </c>
       <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="M4" s="66" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="5" spans="1:13" s="19" customFormat="1" ht="75">
       <c r="A5" s="11" t="s">
@@ -2847,7 +2863,9 @@
       <c r="J5" s="10"/>
       <c r="K5" s="12"/>
       <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="M5" s="66" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="6" spans="1:13" s="19" customFormat="1" ht="90">
       <c r="A6" s="11" t="s">
@@ -2880,7 +2898,9 @@
       <c r="J6" s="10"/>
       <c r="K6" s="12"/>
       <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
+      <c r="M6" s="66" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="90">
       <c r="A7" s="11" t="s">
@@ -2913,7 +2933,9 @@
       <c r="J7" s="10"/>
       <c r="K7" s="12"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="M7" s="66" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="75">
       <c r="A8" s="11" t="s">
@@ -2946,7 +2968,9 @@
       <c r="J8" s="10"/>
       <c r="K8" s="12"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
+      <c r="M8" s="66" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="75">
       <c r="A9" s="11" t="s">
@@ -2979,7 +3003,9 @@
       <c r="J9" s="10"/>
       <c r="K9" s="12"/>
       <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
+      <c r="M9" s="66" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="90">
       <c r="A10" s="11" t="s">
@@ -3012,7 +3038,9 @@
       <c r="J10" s="10"/>
       <c r="K10" s="12"/>
       <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
+      <c r="M10" s="66" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="11" spans="1:13" ht="90">
       <c r="A11" s="11" t="s">
@@ -3045,7 +3073,9 @@
       <c r="J11" s="10"/>
       <c r="K11" s="12"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
+      <c r="M11" s="66" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="90">
       <c r="A12" s="11" t="s">
@@ -3078,7 +3108,9 @@
       <c r="J12" s="10"/>
       <c r="K12" s="12"/>
       <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
+      <c r="M12" s="66" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="90">
       <c r="A13" s="11" t="s">
@@ -3111,7 +3143,9 @@
       <c r="J13" s="10"/>
       <c r="K13" s="12"/>
       <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
+      <c r="M13" s="66" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="150">
       <c r="A14" s="11" t="s">
@@ -3144,7 +3178,9 @@
       <c r="J14" s="10"/>
       <c r="K14" s="12"/>
       <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
+      <c r="M14" s="66" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="15" spans="1:13" ht="120">
       <c r="A15" s="11" t="s">
@@ -3177,7 +3213,9 @@
       <c r="J15" s="10"/>
       <c r="K15" s="12"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
+      <c r="M15" s="66" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="16" spans="1:13" ht="180">
       <c r="A16" s="11" t="s">
@@ -3210,7 +3248,9 @@
       <c r="J16" s="10"/>
       <c r="K16" s="12"/>
       <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+      <c r="M16" s="66" t="s">
+        <v>82</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2">
@@ -3516,6 +3556,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3620,13 +3661,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="61" t="s">
         <v>149</v>
       </c>
       <c r="D2" s="11" t="s">
@@ -3640,9 +3681,9 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="61"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
       <c r="D3" s="11" t="s">
         <v>90</v>
       </c>
@@ -3654,9 +3695,9 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="62"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
       <c r="D4" s="11" t="s">
         <v>102</v>
       </c>
@@ -3668,13 +3709,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="C5" s="61" t="s">
         <v>160</v>
       </c>
       <c r="D5" s="11" t="s">
@@ -3688,9 +3729,9 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="61"/>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
       <c r="D6" s="11" t="s">
         <v>113</v>
       </c>
@@ -3702,9 +3743,9 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="62"/>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
       <c r="D7" s="11" t="s">
         <v>91</v>
       </c>
@@ -3716,13 +3757,13 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="61" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="61" t="s">
         <v>161</v>
       </c>
       <c r="D8" s="11" t="s">
@@ -3736,9 +3777,9 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="61"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
+      <c r="A9" s="62"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
       <c r="D9" s="11" t="s">
         <v>93</v>
       </c>
@@ -3750,9 +3791,9 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="62"/>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="11" t="s">
         <v>94</v>
       </c>
@@ -3764,13 +3805,13 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="C11" s="60" t="s">
+      <c r="C11" s="61" t="s">
         <v>162</v>
       </c>
       <c r="D11" s="11" t="s">
@@ -3784,9 +3825,9 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="61"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
       <c r="D12" s="11" t="s">
         <v>96</v>
       </c>
@@ -3798,9 +3839,9 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="62"/>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
       <c r="D13" s="11" t="s">
         <v>97</v>
       </c>
@@ -3812,13 +3853,13 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="B14" s="60" t="s">
+      <c r="B14" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="61" t="s">
         <v>163</v>
       </c>
       <c r="D14" s="11" t="s">
@@ -3832,9 +3873,9 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="61"/>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
+      <c r="A15" s="62"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
       <c r="D15" s="11" t="s">
         <v>99</v>
       </c>
@@ -3846,9 +3887,9 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="62"/>
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
+      <c r="A16" s="63"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
       <c r="D16" s="11" t="s">
         <v>100</v>
       </c>
@@ -3925,17 +3966,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.5">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="58" t="s">

--- a/Day1/BiswayanNath_ManualTesting.xlsx
+++ b/Day1/BiswayanNath_ManualTesting.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\biswa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\biswa\Downloads\Capg\Sprint\Day1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C578829D-D683-4E2C-976D-6B03242CB770}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEB759B-EB46-449B-8A76-453340D8D1F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -648,9 +648,6 @@
     <t>Make My Trip Application</t>
   </si>
   <si>
-    <t>It does not accept the invalid data (destination location) and replaces it with default location.</t>
-  </si>
-  <si>
     <t>abc@gmail.com</t>
   </si>
   <si>
@@ -674,6 +671,9 @@
     i. With Flight
     ii. ₹0 - ₹20000
     iii. 5 Star</t>
+  </si>
+  <si>
+    <t>It does not accept the invalid data (destination location).</t>
   </si>
 </sst>
 </file>
@@ -1264,6 +1264,9 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1278,9 +1281,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2740,7 +2740,7 @@
         <v>111</v>
       </c>
       <c r="F2" s="60" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>119</v>
@@ -2754,7 +2754,7 @@
       <c r="J2" s="10"/>
       <c r="K2" s="12"/>
       <c r="L2" s="10"/>
-      <c r="M2" s="66" t="s">
+      <c r="M2" s="61" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2775,13 +2775,13 @@
         <v>110</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3" s="17" t="s">
         <v>120</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>30</v>
@@ -2789,7 +2789,7 @@
       <c r="J3" s="10"/>
       <c r="K3" s="12"/>
       <c r="L3" s="10"/>
-      <c r="M3" s="66" t="s">
+      <c r="M3" s="61" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
         <v>188</v>
       </c>
       <c r="F4" s="60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>189</v>
@@ -2828,7 +2828,7 @@
         <v>190</v>
       </c>
       <c r="L4" s="10"/>
-      <c r="M4" s="66" t="s">
+      <c r="M4" s="61" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       <c r="J5" s="10"/>
       <c r="K5" s="12"/>
       <c r="L5" s="10"/>
-      <c r="M5" s="66" t="s">
+      <c r="M5" s="61" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       <c r="J6" s="10"/>
       <c r="K6" s="12"/>
       <c r="L6" s="10"/>
-      <c r="M6" s="66" t="s">
+      <c r="M6" s="61" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       <c r="J7" s="10"/>
       <c r="K7" s="12"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="66" t="s">
+      <c r="M7" s="61" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       <c r="J8" s="10"/>
       <c r="K8" s="12"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="66" t="s">
+      <c r="M8" s="61" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       <c r="J9" s="10"/>
       <c r="K9" s="12"/>
       <c r="L9" s="10"/>
-      <c r="M9" s="66" t="s">
+      <c r="M9" s="61" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       <c r="J10" s="10"/>
       <c r="K10" s="12"/>
       <c r="L10" s="10"/>
-      <c r="M10" s="66" t="s">
+      <c r="M10" s="61" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       <c r="J11" s="10"/>
       <c r="K11" s="12"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="66" t="s">
+      <c r="M11" s="61" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       <c r="J12" s="10"/>
       <c r="K12" s="12"/>
       <c r="L12" s="10"/>
-      <c r="M12" s="66" t="s">
+      <c r="M12" s="61" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       <c r="J13" s="10"/>
       <c r="K13" s="12"/>
       <c r="L13" s="10"/>
-      <c r="M13" s="66" t="s">
+      <c r="M13" s="61" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       <c r="J14" s="10"/>
       <c r="K14" s="12"/>
       <c r="L14" s="10"/>
-      <c r="M14" s="66" t="s">
+      <c r="M14" s="61" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       <c r="J15" s="10"/>
       <c r="K15" s="12"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="66" t="s">
+      <c r="M15" s="61" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       <c r="J16" s="10"/>
       <c r="K16" s="12"/>
       <c r="L16" s="10"/>
-      <c r="M16" s="66" t="s">
+      <c r="M16" s="61" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F2" s="56" t="s">
         <v>194</v>
@@ -3661,13 +3661,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="62" t="s">
         <v>149</v>
       </c>
       <c r="D2" s="11" t="s">
@@ -3681,9 +3681,9 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="62"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
       <c r="D3" s="11" t="s">
         <v>90</v>
       </c>
@@ -3695,9 +3695,9 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
       <c r="D4" s="11" t="s">
         <v>102</v>
       </c>
@@ -3709,13 +3709,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="62" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="62" t="s">
         <v>160</v>
       </c>
       <c r="D5" s="11" t="s">
@@ -3729,9 +3729,9 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="62"/>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
+      <c r="A6" s="63"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
       <c r="D6" s="11" t="s">
         <v>113</v>
       </c>
@@ -3743,9 +3743,9 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="63"/>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
       <c r="D7" s="11" t="s">
         <v>91</v>
       </c>
@@ -3757,13 +3757,13 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="61" t="s">
+      <c r="A8" s="62" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="62" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="62" t="s">
         <v>161</v>
       </c>
       <c r="D8" s="11" t="s">
@@ -3777,9 +3777,9 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="62"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
       <c r="D9" s="11" t="s">
         <v>93</v>
       </c>
@@ -3791,9 +3791,9 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="63"/>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
+      <c r="A10" s="64"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
       <c r="D10" s="11" t="s">
         <v>94</v>
       </c>
@@ -3805,13 +3805,13 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="62" t="s">
         <v>162</v>
       </c>
       <c r="D11" s="11" t="s">
@@ -3825,9 +3825,9 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="62"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
       <c r="D12" s="11" t="s">
         <v>96</v>
       </c>
@@ -3839,9 +3839,9 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="63"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
+      <c r="A13" s="64"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="11" t="s">
         <v>97</v>
       </c>
@@ -3853,13 +3853,13 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="62" t="s">
         <v>163</v>
       </c>
       <c r="D14" s="11" t="s">
@@ -3873,9 +3873,9 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="62"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
+      <c r="A15" s="63"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
       <c r="D15" s="11" t="s">
         <v>99</v>
       </c>
@@ -3887,9 +3887,9 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="63"/>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
+      <c r="A16" s="64"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
       <c r="D16" s="11" t="s">
         <v>100</v>
       </c>
@@ -3966,17 +3966,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.5">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="58" t="s">
